--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53.32436398628737</v>
+        <v>50.94942281238824</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42.17764185874911</v>
+        <v>37.34366692878324</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54.3498325244852</v>
+        <v>51.92921940493417</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>40.17980142969954</v>
+        <v>34.81001159107367</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46.83926952653145</v>
+        <v>43.25552938343893</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.413553596105404</v>
+        <v>2.400191591470429</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>303977.9146917594</v>
+        <v>341876.7800376925</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.72090948271298</v>
+        <v>3.100552436103905</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>783.7933333333334</v>
+        <v>644.968679037019</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>899.8666666666667</v>
+        <v>790.6394326974544</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200.24</v>
+        <v>182.6007125288791</v>
       </c>
     </row>
     <row r="5">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>257.6298281428261</v>
+        <v>246.1556043407702</v>
       </c>
     </row>
     <row r="7">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>156.7264585669278</v>
+        <v>149.7462324251643</v>
       </c>
     </row>
     <row r="8">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-382.1996442889462</v>
+        <v>-365.1773752168793</v>
       </c>
     </row>
     <row r="9">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-5.496511364740391</v>
+        <v>-5.251709736046172</v>
       </c>
     </row>
     <row r="10">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>1996.936131056067</v>
+        <v>1730.057576076361</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>40.17980142969954</v>
+        <v>34.81001159107367</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41.16766192601074</v>
+        <v>35.64189398436356</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.9878604963111925</v>
+        <v>-0.8318823932898951</v>
       </c>
     </row>
   </sheetData>
@@ -843,13 +843,13 @@
         <v>81500</v>
       </c>
       <c r="D2" t="n">
-        <v>3.874698723992094</v>
+        <v>3.885767508406123</v>
       </c>
       <c r="E2" t="n">
-        <v>2.832289106794466</v>
+        <v>2.840037255884286</v>
       </c>
       <c r="F2" t="n">
-        <v>2.759350297391811</v>
+        <v>2.766898911494779</v>
       </c>
     </row>
     <row r="3">
@@ -865,13 +865,13 @@
         <v>99000</v>
       </c>
       <c r="D3" t="n">
-        <v>4.870090738076601</v>
+        <v>4.88115952249063</v>
       </c>
       <c r="E3" t="n">
-        <v>3.529063516653621</v>
+        <v>3.536811665743441</v>
       </c>
       <c r="F3" t="n">
-        <v>3.349638854350216</v>
+        <v>3.356993072011102</v>
       </c>
     </row>
     <row r="4">
@@ -887,13 +887,13 @@
         <v>92000</v>
       </c>
       <c r="D4" t="n">
-        <v>4.418352343710404</v>
+        <v>4.429421128124432</v>
       </c>
       <c r="E4" t="n">
-        <v>3.212846640597283</v>
+        <v>3.220594789687103</v>
       </c>
       <c r="F4" t="n">
-        <v>2.970966547068136</v>
+        <v>2.978131374500818</v>
       </c>
     </row>
     <row r="5">
@@ -909,13 +909,13 @@
         <v>67500</v>
       </c>
       <c r="D5" t="n">
-        <v>3.131717319062516</v>
+        <v>3.142786103476546</v>
       </c>
       <c r="E5" t="n">
-        <v>2.312202123343762</v>
+        <v>2.319950272433582</v>
       </c>
       <c r="F5" t="n">
-        <v>2.083064975985371</v>
+        <v>2.090045290480704</v>
       </c>
     </row>
     <row r="6">
@@ -931,13 +931,13 @@
         <v>60000</v>
       </c>
       <c r="D6" t="n">
-        <v>2.754081121879418</v>
+        <v>2.765149906293447</v>
       </c>
       <c r="E6" t="n">
-        <v>2.047856785315592</v>
+        <v>2.055604934405413</v>
       </c>
       <c r="F6" t="n">
-        <v>1.797404637818423</v>
+        <v>1.80420519106434</v>
       </c>
     </row>
     <row r="7">
@@ -953,13 +953,13 @@
         <v>78000</v>
       </c>
       <c r="D7" t="n">
-        <v>3.589690273287869</v>
+        <v>3.600759057701898</v>
       </c>
       <c r="E7" t="n">
-        <v>2.632783191301508</v>
+        <v>2.640531340391328</v>
       </c>
       <c r="F7" t="n">
-        <v>2.251285781177124</v>
+        <v>2.257911202493236</v>
       </c>
     </row>
     <row r="8">
@@ -975,13 +975,13 @@
         <v>81500</v>
       </c>
       <c r="D8" t="n">
-        <v>3.863832776808995</v>
+        <v>3.874901561223024</v>
       </c>
       <c r="E8" t="n">
-        <v>2.824682943766297</v>
+        <v>2.832431092856117</v>
       </c>
       <c r="F8" t="n">
-        <v>2.353176456773429</v>
+        <v>2.359631256262332</v>
       </c>
     </row>
     <row r="9">
@@ -997,13 +997,13 @@
         <v>56500</v>
       </c>
       <c r="D9" t="n">
-        <v>2.565619283851249</v>
+        <v>2.576688068265278</v>
       </c>
       <c r="E9" t="n">
-        <v>1.915933498695875</v>
+        <v>1.923681647785694</v>
       </c>
       <c r="F9" t="n">
-        <v>1.555014608145341</v>
+        <v>1.561303179762758</v>
       </c>
     </row>
     <row r="10">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>19.11990215870985</v>
+        <v>19.17511947807007</v>
       </c>
     </row>
     <row r="11">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>35.0558108193709</v>
+        <v>30.45373593466163</v>
       </c>
       <c r="F11" t="n">
-        <v>27.7193673678216</v>
+        <v>24.08040990536886</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>46.83926952653145</v>
+        <v>43.25552938343893</v>
       </c>
     </row>
     <row r="13">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.04668791393023</v>
+        <v>29.17834281516769</v>
       </c>
       <c r="C2" t="n">
-        <v>36.64058076996021</v>
+        <v>32.289420755596</v>
       </c>
       <c r="D2" t="n">
-        <v>40.23447362599018</v>
+        <v>35.40049869602431</v>
       </c>
       <c r="E2" t="n">
-        <v>43.82836648202016</v>
+        <v>38.51157663645262</v>
       </c>
       <c r="F2" t="n">
-        <v>47.42225933805013</v>
+        <v>41.62265457688093</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.0182720303097</v>
+        <v>30.14992693154716</v>
       </c>
       <c r="C3" t="n">
-        <v>37.61216488633968</v>
+        <v>33.26100487197547</v>
       </c>
       <c r="D3" t="n">
-        <v>41.20605774236965</v>
+        <v>36.37208281240378</v>
       </c>
       <c r="E3" t="n">
-        <v>44.79995059839962</v>
+        <v>39.48316075283209</v>
       </c>
       <c r="F3" t="n">
-        <v>48.39384345442959</v>
+        <v>42.59423869326041</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34.98985614668917</v>
+        <v>31.12151104792662</v>
       </c>
       <c r="C4" t="n">
-        <v>38.58374900271914</v>
+        <v>34.23258898835493</v>
       </c>
       <c r="D4" t="n">
-        <v>42.17764185874911</v>
+        <v>37.34366692878324</v>
       </c>
       <c r="E4" t="n">
-        <v>45.77153471477909</v>
+        <v>40.45474486921156</v>
       </c>
       <c r="F4" t="n">
-        <v>49.36542757080906</v>
+        <v>43.56582280963987</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35.96144026306864</v>
+        <v>32.09309516430609</v>
       </c>
       <c r="C5" t="n">
-        <v>39.55533311909861</v>
+        <v>35.2041731047344</v>
       </c>
       <c r="D5" t="n">
-        <v>43.14922597512858</v>
+        <v>38.31525104516271</v>
       </c>
       <c r="E5" t="n">
-        <v>46.74311883115855</v>
+        <v>41.42632898559103</v>
       </c>
       <c r="F5" t="n">
-        <v>50.33701168718852</v>
+        <v>44.53740692601934</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.93302437944811</v>
+        <v>33.06467928068555</v>
       </c>
       <c r="C6" t="n">
-        <v>40.52691723547808</v>
+        <v>36.17575722111387</v>
       </c>
       <c r="D6" t="n">
-        <v>44.12081009150805</v>
+        <v>39.28683516154218</v>
       </c>
       <c r="E6" t="n">
-        <v>47.71470294753803</v>
+        <v>42.39791310197049</v>
       </c>
       <c r="F6" t="n">
-        <v>51.308595803568</v>
+        <v>45.5089910423988</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>42.96</v>
+        <v>38.13</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>44.13</v>
+        <v>39.31</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>44.53</v>
+        <v>39.7</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50.94942281238824</v>
+        <v>50.93591183222913</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37.34366692878324</v>
+        <v>37.3193181236258</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51.92921940493417</v>
+        <v>51.91544859823353</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.81001159107367</v>
+        <v>34.7836630206761</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43.25552938343893</v>
+        <v>43.23584669717509</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.400191591470429</v>
+        <v>2.400339014600914</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>341876.7800376925</v>
+        <v>342121.2181010839</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.100552436103905</v>
+        <v>3.102225655871853</v>
       </c>
     </row>
   </sheetData>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>790.6394326974544</v>
+        <v>789.3366637191217</v>
       </c>
     </row>
     <row r="4">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>246.1556043407702</v>
+        <v>246.0903277723083</v>
       </c>
     </row>
     <row r="7">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>149.7462324251643</v>
+        <v>149.7065220955174</v>
       </c>
     </row>
     <row r="8">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-365.1773752168793</v>
+        <v>-365.0805359594596</v>
       </c>
     </row>
     <row r="9">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-5.251709736046172</v>
+        <v>-5.250317065783618</v>
       </c>
     </row>
     <row r="10">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>1730.057576076361</v>
+        <v>1728.748052127602</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34.81001159107367</v>
+        <v>34.7836630206761</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35.64189398436356</v>
+        <v>35.61526484030516</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.8318823932898951</v>
+        <v>-0.8316018196290571</v>
       </c>
     </row>
   </sheetData>
@@ -843,13 +843,13 @@
         <v>81500</v>
       </c>
       <c r="D2" t="n">
-        <v>3.885767508406123</v>
+        <v>3.885830478440179</v>
       </c>
       <c r="E2" t="n">
-        <v>2.840037255884286</v>
+        <v>2.840081334908125</v>
       </c>
       <c r="F2" t="n">
-        <v>2.766898911494779</v>
+        <v>2.766941855369134</v>
       </c>
     </row>
     <row r="3">
@@ -865,13 +865,13 @@
         <v>99000</v>
       </c>
       <c r="D3" t="n">
-        <v>4.88115952249063</v>
+        <v>4.881222492524686</v>
       </c>
       <c r="E3" t="n">
-        <v>3.536811665743441</v>
+        <v>3.53685574476728</v>
       </c>
       <c r="F3" t="n">
-        <v>3.356993072011102</v>
+        <v>3.357034909969024</v>
       </c>
     </row>
     <row r="4">
@@ -887,13 +887,13 @@
         <v>92000</v>
       </c>
       <c r="D4" t="n">
-        <v>4.429421128124432</v>
+        <v>4.429484098158489</v>
       </c>
       <c r="E4" t="n">
-        <v>3.220594789687103</v>
+        <v>3.220638868710942</v>
       </c>
       <c r="F4" t="n">
-        <v>2.978131374500818</v>
+        <v>2.978172135022531</v>
       </c>
     </row>
     <row r="5">
@@ -909,13 +909,13 @@
         <v>67500</v>
       </c>
       <c r="D5" t="n">
-        <v>3.142786103476546</v>
+        <v>3.142849073510602</v>
       </c>
       <c r="E5" t="n">
-        <v>2.319950272433582</v>
+        <v>2.319994351457421</v>
       </c>
       <c r="F5" t="n">
-        <v>2.090045290480704</v>
+        <v>2.090085001312992</v>
       </c>
     </row>
     <row r="6">
@@ -931,13 +931,13 @@
         <v>60000</v>
       </c>
       <c r="D6" t="n">
-        <v>2.765149906293447</v>
+        <v>2.765212876327503</v>
       </c>
       <c r="E6" t="n">
-        <v>2.055604934405413</v>
+        <v>2.055649013429252</v>
       </c>
       <c r="F6" t="n">
-        <v>1.80420519106434</v>
+        <v>1.804243879239434</v>
       </c>
     </row>
     <row r="7">
@@ -953,13 +953,13 @@
         <v>78000</v>
       </c>
       <c r="D7" t="n">
-        <v>3.600759057701898</v>
+        <v>3.600822027735954</v>
       </c>
       <c r="E7" t="n">
-        <v>2.640531340391328</v>
+        <v>2.640575419415168</v>
       </c>
       <c r="F7" t="n">
-        <v>2.257911202493236</v>
+        <v>2.25794889434722</v>
       </c>
     </row>
     <row r="8">
@@ -975,13 +975,13 @@
         <v>81500</v>
       </c>
       <c r="D8" t="n">
-        <v>3.874901561223024</v>
+        <v>3.87496453125708</v>
       </c>
       <c r="E8" t="n">
-        <v>2.832431092856117</v>
+        <v>2.832475171879956</v>
       </c>
       <c r="F8" t="n">
-        <v>2.359631256262332</v>
+        <v>2.359667977453064</v>
       </c>
     </row>
     <row r="9">
@@ -997,13 +997,13 @@
         <v>56500</v>
       </c>
       <c r="D9" t="n">
-        <v>2.576688068265278</v>
+        <v>2.576751038299335</v>
       </c>
       <c r="E9" t="n">
-        <v>1.923681647785694</v>
+        <v>1.923725726809534</v>
       </c>
       <c r="F9" t="n">
-        <v>1.561303179762758</v>
+        <v>1.561338955287342</v>
       </c>
     </row>
     <row r="10">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>19.17511947807007</v>
+        <v>19.17543360800074</v>
       </c>
     </row>
     <row r="11">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>30.45373593466163</v>
+        <v>30.42844659107011</v>
       </c>
       <c r="F11" t="n">
-        <v>24.08040990536886</v>
+        <v>24.06041308917435</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>43.25552938343893</v>
+        <v>43.23584669717509</v>
       </c>
     </row>
     <row r="13">
@@ -1066,9 +1066,9 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.17834281516769</v>
+        <v>29.15885714250565</v>
       </c>
       <c r="C2" t="n">
-        <v>32.289420755596</v>
+        <v>32.26750351668625</v>
       </c>
       <c r="D2" t="n">
-        <v>35.40049869602431</v>
+        <v>35.37614989086686</v>
       </c>
       <c r="E2" t="n">
-        <v>38.51157663645262</v>
+        <v>38.48479626504746</v>
       </c>
       <c r="F2" t="n">
-        <v>41.62265457688093</v>
+        <v>41.59344263922807</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.14992693154716</v>
+        <v>30.13044125888511</v>
       </c>
       <c r="C3" t="n">
-        <v>33.26100487197547</v>
+        <v>33.23908763306572</v>
       </c>
       <c r="D3" t="n">
-        <v>36.37208281240378</v>
+        <v>36.34773400724633</v>
       </c>
       <c r="E3" t="n">
-        <v>39.48316075283209</v>
+        <v>39.45638038142693</v>
       </c>
       <c r="F3" t="n">
-        <v>42.59423869326041</v>
+        <v>42.56502675560753</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.12151104792662</v>
+        <v>31.10202537526458</v>
       </c>
       <c r="C4" t="n">
-        <v>34.23258898835493</v>
+        <v>34.2106717494452</v>
       </c>
       <c r="D4" t="n">
-        <v>37.34366692878324</v>
+        <v>37.3193181236258</v>
       </c>
       <c r="E4" t="n">
-        <v>40.45474486921156</v>
+        <v>40.4279644978064</v>
       </c>
       <c r="F4" t="n">
-        <v>43.56582280963987</v>
+        <v>43.536610871987</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.09309516430609</v>
+        <v>32.07360949164405</v>
       </c>
       <c r="C5" t="n">
-        <v>35.2041731047344</v>
+        <v>35.18225586582466</v>
       </c>
       <c r="D5" t="n">
-        <v>38.31525104516271</v>
+        <v>38.29090224000526</v>
       </c>
       <c r="E5" t="n">
-        <v>41.42632898559103</v>
+        <v>41.39954861418587</v>
       </c>
       <c r="F5" t="n">
-        <v>44.53740692601934</v>
+        <v>44.50819498836647</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.06467928068555</v>
+        <v>33.04519360802352</v>
       </c>
       <c r="C6" t="n">
-        <v>36.17575722111387</v>
+        <v>36.15383998220413</v>
       </c>
       <c r="D6" t="n">
-        <v>39.28683516154218</v>
+        <v>39.26248635638473</v>
       </c>
       <c r="E6" t="n">
-        <v>42.39791310197049</v>
+        <v>42.37113273056534</v>
       </c>
       <c r="F6" t="n">
-        <v>45.5089910423988</v>
+        <v>45.47977910474594</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>38.13</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>39.31</v>
+        <v>39.28</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>39.7</v>
+        <v>39.67</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50.93591183222913</v>
+        <v>53.94635482641601</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>342121.2181010839</v>
+        <v>393377.5927074145</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.102225655871853</v>
+        <v>3.566999051726406</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53.94635482641601</v>
+        <v>55.04670112689429</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>393377.5927074145</v>
+        <v>412112.297959403</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.566999051726406</v>
+        <v>3.736878264744828</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55.04670112689429</v>
+        <v>53.91370360088253</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>412112.297959403</v>
+        <v>392821.6667355453</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.736878264744828</v>
+        <v>3.561958125524079</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53.91370360088253</v>
+        <v>53.90889664553365</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37.3193181236258</v>
+        <v>37.31376832138561</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51.91544859823353</v>
+        <v>51.91081980765414</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.7836630206761</v>
+        <v>34.77481233396326</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43.23584669717509</v>
+        <v>43.23799895870444</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.400339014600914</v>
+        <v>2.400432119778173</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>392821.6667355453</v>
+        <v>392864.5527337283</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.561958125524079</v>
+        <v>3.562072811459983</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>182.6007125288791</v>
+        <v>182.1631039520335</v>
       </c>
     </row>
     <row r="5">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>246.0903277723083</v>
+        <v>246.0683863151577</v>
       </c>
     </row>
     <row r="7">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>149.7065220955174</v>
+        <v>149.6931742355285</v>
       </c>
     </row>
     <row r="8">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-365.0805359594596</v>
+        <v>-365.047985314301</v>
       </c>
     </row>
     <row r="9">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-5.250317065783618</v>
+        <v>-5.249848946585399</v>
       </c>
     </row>
     <row r="10">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>1728.748052127602</v>
+        <v>1728.308172997974</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34.7836630206761</v>
+        <v>34.77481233396326</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35.61526484030516</v>
+        <v>35.60653865806835</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.8316018196290571</v>
+        <v>-0.8317263241050838</v>
       </c>
     </row>
   </sheetData>
@@ -843,13 +843,13 @@
         <v>81500</v>
       </c>
       <c r="D2" t="n">
-        <v>3.885830478440179</v>
+        <v>3.885851644600359</v>
       </c>
       <c r="E2" t="n">
-        <v>2.840081334908125</v>
+        <v>2.840096151220251</v>
       </c>
       <c r="F2" t="n">
-        <v>2.766941855369134</v>
+        <v>2.766956290122695</v>
       </c>
     </row>
     <row r="3">
@@ -865,13 +865,13 @@
         <v>99000</v>
       </c>
       <c r="D3" t="n">
-        <v>4.881222492524686</v>
+        <v>4.881243658684866</v>
       </c>
       <c r="E3" t="n">
-        <v>3.53685574476728</v>
+        <v>3.536870561079406</v>
       </c>
       <c r="F3" t="n">
-        <v>3.357034909969024</v>
+        <v>3.357048972990146</v>
       </c>
     </row>
     <row r="4">
@@ -887,13 +887,13 @@
         <v>92000</v>
       </c>
       <c r="D4" t="n">
-        <v>4.429484098158489</v>
+        <v>4.429505264318669</v>
       </c>
       <c r="E4" t="n">
-        <v>3.220638868710942</v>
+        <v>3.220653685023068</v>
       </c>
       <c r="F4" t="n">
-        <v>2.978172135022531</v>
+        <v>2.97818583588429</v>
       </c>
     </row>
     <row r="5">
@@ -909,13 +909,13 @@
         <v>67500</v>
       </c>
       <c r="D5" t="n">
-        <v>3.142849073510602</v>
+        <v>3.142870239670782</v>
       </c>
       <c r="E5" t="n">
-        <v>2.319994351457421</v>
+        <v>2.320009167769547</v>
       </c>
       <c r="F5" t="n">
-        <v>2.090085001312992</v>
+        <v>2.090098349341934</v>
       </c>
     </row>
     <row r="6">
@@ -931,13 +931,13 @@
         <v>60000</v>
       </c>
       <c r="D6" t="n">
-        <v>2.765212876327503</v>
+        <v>2.765234042487683</v>
       </c>
       <c r="E6" t="n">
-        <v>2.055649013429252</v>
+        <v>2.055663829741378</v>
       </c>
       <c r="F6" t="n">
-        <v>1.804243879239434</v>
+        <v>1.804256883521922</v>
       </c>
     </row>
     <row r="7">
@@ -953,13 +953,13 @@
         <v>78000</v>
       </c>
       <c r="D7" t="n">
-        <v>3.600822027735954</v>
+        <v>3.600843193896134</v>
       </c>
       <c r="E7" t="n">
-        <v>2.640575419415168</v>
+        <v>2.640590235727294</v>
       </c>
       <c r="F7" t="n">
-        <v>2.25794889434722</v>
+        <v>2.257961563735619</v>
       </c>
     </row>
     <row r="8">
@@ -975,13 +975,13 @@
         <v>81500</v>
       </c>
       <c r="D8" t="n">
-        <v>3.87496453125708</v>
+        <v>3.874985697417261</v>
       </c>
       <c r="E8" t="n">
-        <v>2.832475171879956</v>
+        <v>2.832489988192082</v>
       </c>
       <c r="F8" t="n">
-        <v>2.359667977453064</v>
+        <v>2.359680320571766</v>
       </c>
     </row>
     <row r="9">
@@ -997,13 +997,13 @@
         <v>56500</v>
       </c>
       <c r="D9" t="n">
-        <v>2.576751038299335</v>
+        <v>2.576772204459514</v>
       </c>
       <c r="E9" t="n">
-        <v>1.923725726809534</v>
+        <v>1.92374054312166</v>
       </c>
       <c r="F9" t="n">
-        <v>1.561338955287342</v>
+        <v>1.561350980538641</v>
       </c>
     </row>
     <row r="10">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>19.17543360800074</v>
+        <v>19.17553919670701</v>
       </c>
     </row>
     <row r="11">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>30.42844659107011</v>
+        <v>30.43103495372438</v>
       </c>
       <c r="F11" t="n">
-        <v>24.06041308917435</v>
+        <v>24.06245976199742</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>43.23584669717509</v>
+        <v>43.23799895870444</v>
       </c>
     </row>
     <row r="13">
@@ -1066,9 +1066,9 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.15885714250565</v>
+        <v>29.15441507265919</v>
       </c>
       <c r="C2" t="n">
-        <v>32.26750351668625</v>
+        <v>32.26250758064293</v>
       </c>
       <c r="D2" t="n">
-        <v>35.37614989086686</v>
+        <v>35.37060008862668</v>
       </c>
       <c r="E2" t="n">
-        <v>38.48479626504746</v>
+        <v>38.47869259661043</v>
       </c>
       <c r="F2" t="n">
-        <v>41.59344263922807</v>
+        <v>41.58678510459416</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.13044125888511</v>
+        <v>30.12599918903866</v>
       </c>
       <c r="C3" t="n">
-        <v>33.23908763306572</v>
+        <v>33.2340916970224</v>
       </c>
       <c r="D3" t="n">
-        <v>36.34773400724633</v>
+        <v>36.34218420500615</v>
       </c>
       <c r="E3" t="n">
-        <v>39.45638038142693</v>
+        <v>39.4502767129899</v>
       </c>
       <c r="F3" t="n">
-        <v>42.56502675560753</v>
+        <v>42.55836922097363</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.10202537526458</v>
+        <v>31.09758330541812</v>
       </c>
       <c r="C4" t="n">
-        <v>34.2106717494452</v>
+        <v>34.20567581340187</v>
       </c>
       <c r="D4" t="n">
-        <v>37.3193181236258</v>
+        <v>37.31376832138561</v>
       </c>
       <c r="E4" t="n">
-        <v>40.4279644978064</v>
+        <v>40.42186082936936</v>
       </c>
       <c r="F4" t="n">
-        <v>43.536610871987</v>
+        <v>43.5299533373531</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.07360949164405</v>
+        <v>32.06916742179759</v>
       </c>
       <c r="C5" t="n">
-        <v>35.18225586582466</v>
+        <v>35.17725992978134</v>
       </c>
       <c r="D5" t="n">
-        <v>38.29090224000526</v>
+        <v>38.28535243776508</v>
       </c>
       <c r="E5" t="n">
-        <v>41.39954861418587</v>
+        <v>41.39344494574883</v>
       </c>
       <c r="F5" t="n">
-        <v>44.50819498836647</v>
+        <v>44.50153745373257</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.04519360802352</v>
+        <v>33.04075153817706</v>
       </c>
       <c r="C6" t="n">
-        <v>36.15383998220413</v>
+        <v>36.1488440461608</v>
       </c>
       <c r="D6" t="n">
-        <v>39.26248635638473</v>
+        <v>39.25693655414454</v>
       </c>
       <c r="E6" t="n">
-        <v>42.37113273056534</v>
+        <v>42.3650290621283</v>
       </c>
       <c r="F6" t="n">
-        <v>45.47977910474594</v>
+        <v>45.47312157011203</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53.90889664553365</v>
+        <v>55.1691215792289</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>392864.5527337283</v>
+        <v>414323.0336069782</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.562072811459983</v>
+        <v>3.756635214104755</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37.31376832138561</v>
+        <v>38.45129720121868</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43.23799895870444</v>
+        <v>47.02976189148133</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>414323.0336069782</v>
+        <v>316871.9410972099</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.756635214104755</v>
+        <v>2.873053621770589</v>
       </c>
     </row>
   </sheetData>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>30.43103495372438</v>
+        <v>35.22635810376262</v>
       </c>
       <c r="F11" t="n">
-        <v>24.06245976199742</v>
+        <v>27.85422269477431</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>43.23799895870444</v>
+        <v>47.02976189148133</v>
       </c>
     </row>
     <row r="13">
@@ -1064,11 +1064,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.15441507265919</v>
+        <v>29.69942472975451</v>
       </c>
       <c r="C2" t="n">
-        <v>32.26250758064293</v>
+        <v>32.73654523295512</v>
       </c>
       <c r="D2" t="n">
-        <v>35.37060008862668</v>
+        <v>35.77366573615572</v>
       </c>
       <c r="E2" t="n">
-        <v>38.47869259661043</v>
+        <v>38.81078623935633</v>
       </c>
       <c r="F2" t="n">
-        <v>41.58678510459416</v>
+        <v>41.84790674255693</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.12599918903866</v>
+        <v>31.03824046228599</v>
       </c>
       <c r="C3" t="n">
-        <v>33.2340916970224</v>
+        <v>34.0753609654866</v>
       </c>
       <c r="D3" t="n">
-        <v>36.34218420500615</v>
+        <v>37.1124814686872</v>
       </c>
       <c r="E3" t="n">
-        <v>39.4502767129899</v>
+        <v>40.14960197188781</v>
       </c>
       <c r="F3" t="n">
-        <v>42.55836922097363</v>
+        <v>43.18672247508841</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.09758330541812</v>
+        <v>32.37705619481747</v>
       </c>
       <c r="C4" t="n">
-        <v>34.20567581340187</v>
+        <v>35.41417669801807</v>
       </c>
       <c r="D4" t="n">
-        <v>37.31376832138561</v>
+        <v>38.45129720121868</v>
       </c>
       <c r="E4" t="n">
-        <v>40.42186082936936</v>
+        <v>41.48841770441929</v>
       </c>
       <c r="F4" t="n">
-        <v>43.5299533373531</v>
+        <v>44.52553820761989</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.06916742179759</v>
+        <v>33.71587192734895</v>
       </c>
       <c r="C5" t="n">
-        <v>35.17725992978134</v>
+        <v>36.75299243054955</v>
       </c>
       <c r="D5" t="n">
-        <v>38.28535243776508</v>
+        <v>39.79011293375016</v>
       </c>
       <c r="E5" t="n">
-        <v>41.39344494574883</v>
+        <v>42.82723343695076</v>
       </c>
       <c r="F5" t="n">
-        <v>44.50153745373257</v>
+        <v>45.86435394015137</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.04075153817706</v>
+        <v>35.05468765988043</v>
       </c>
       <c r="C6" t="n">
-        <v>36.1488440461608</v>
+        <v>38.09180816308103</v>
       </c>
       <c r="D6" t="n">
-        <v>39.25693655414454</v>
+        <v>41.12892866628164</v>
       </c>
       <c r="E6" t="n">
-        <v>42.3650290621283</v>
+        <v>44.16604916948225</v>
       </c>
       <c r="F6" t="n">
-        <v>45.47312157011203</v>
+        <v>47.20316967268285</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>38.1</v>
+        <v>38.54</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>39.28</v>
+        <v>38.69</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>39.67</v>
+        <v>38.73</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55.1691215792289</v>
+        <v>55.27902324271707</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38.45129720121868</v>
+        <v>38.62793598283244</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51.91081980765414</v>
+        <v>52.01423065210093</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.77481233396326</v>
+        <v>34.97325064431904</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47.02976189148133</v>
+        <v>47.15553510603037</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.400432119778173</v>
+        <v>2.349869181366118</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>316871.9410972099</v>
+        <v>316781.2469394869</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.873053621770589</v>
+        <v>2.865576440650295</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>644.968679037019</v>
+        <v>654.780337115778</v>
       </c>
     </row>
     <row r="3">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>246.0683863151577</v>
+        <v>246.5585758308463</v>
       </c>
     </row>
     <row r="7">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>149.6931742355285</v>
+        <v>149.9913759902489</v>
       </c>
     </row>
     <row r="8">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-365.047985314301</v>
+        <v>-365.7751924854616</v>
       </c>
     </row>
     <row r="9">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-5.249848946585399</v>
+        <v>-5.260307099910584</v>
       </c>
     </row>
     <row r="10">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>1728.308172997974</v>
+        <v>1738.170557022656</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34.77481233396326</v>
+        <v>34.97325064431904</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35.60653865806835</v>
+        <v>35.81455261470462</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.8317263241050838</v>
+        <v>-0.8413019703855866</v>
       </c>
     </row>
   </sheetData>
@@ -843,13 +843,13 @@
         <v>81500</v>
       </c>
       <c r="D2" t="n">
-        <v>3.885851644600359</v>
+        <v>3.885378775832521</v>
       </c>
       <c r="E2" t="n">
-        <v>2.840096151220251</v>
+        <v>2.839765143082765</v>
       </c>
       <c r="F2" t="n">
-        <v>2.766956290122695</v>
+        <v>2.766633806305482</v>
       </c>
     </row>
     <row r="3">
@@ -865,13 +865,13 @@
         <v>99000</v>
       </c>
       <c r="D3" t="n">
-        <v>4.881243658684866</v>
+        <v>4.880770789917028</v>
       </c>
       <c r="E3" t="n">
-        <v>3.536870561079406</v>
+        <v>3.536539552941919</v>
       </c>
       <c r="F3" t="n">
-        <v>3.357048972990146</v>
+        <v>3.356734793969791</v>
       </c>
     </row>
     <row r="4">
@@ -887,13 +887,13 @@
         <v>92000</v>
       </c>
       <c r="D4" t="n">
-        <v>4.429505264318669</v>
+        <v>4.429032395550832</v>
       </c>
       <c r="E4" t="n">
-        <v>3.220653685023068</v>
+        <v>3.220322676885582</v>
       </c>
       <c r="F4" t="n">
-        <v>2.97818583588429</v>
+        <v>2.977879747790682</v>
       </c>
     </row>
     <row r="5">
@@ -909,13 +909,13 @@
         <v>67500</v>
       </c>
       <c r="D5" t="n">
-        <v>3.142870239670782</v>
+        <v>3.142397370902944</v>
       </c>
       <c r="E5" t="n">
-        <v>2.320009167769547</v>
+        <v>2.319678159632061</v>
       </c>
       <c r="F5" t="n">
-        <v>2.090098349341934</v>
+        <v>2.089800143812667</v>
       </c>
     </row>
     <row r="6">
@@ -931,13 +931,13 @@
         <v>60000</v>
       </c>
       <c r="D6" t="n">
-        <v>2.765234042487683</v>
+        <v>2.764761173719845</v>
       </c>
       <c r="E6" t="n">
-        <v>2.055663829741378</v>
+        <v>2.055332821603892</v>
       </c>
       <c r="F6" t="n">
-        <v>1.804256883521922</v>
+        <v>1.803966357560469</v>
       </c>
     </row>
     <row r="7">
@@ -953,13 +953,13 @@
         <v>78000</v>
       </c>
       <c r="D7" t="n">
-        <v>3.600843193896134</v>
+        <v>3.600370325128296</v>
       </c>
       <c r="E7" t="n">
-        <v>2.640590235727294</v>
+        <v>2.640259227589807</v>
       </c>
       <c r="F7" t="n">
-        <v>2.257961563735619</v>
+        <v>2.257678519573137</v>
       </c>
     </row>
     <row r="8">
@@ -975,13 +975,13 @@
         <v>81500</v>
       </c>
       <c r="D8" t="n">
-        <v>3.874985697417261</v>
+        <v>3.874512828649423</v>
       </c>
       <c r="E8" t="n">
-        <v>2.832489988192082</v>
+        <v>2.832158980054596</v>
       </c>
       <c r="F8" t="n">
-        <v>2.359680320571766</v>
+        <v>2.359404565532478</v>
       </c>
     </row>
     <row r="9">
@@ -997,13 +997,13 @@
         <v>56500</v>
       </c>
       <c r="D9" t="n">
-        <v>2.576772204459514</v>
+        <v>2.576299335691676</v>
       </c>
       <c r="E9" t="n">
-        <v>1.92374054312166</v>
+        <v>1.923409534984173</v>
       </c>
       <c r="F9" t="n">
-        <v>1.561350980538641</v>
+        <v>1.561082326908671</v>
       </c>
     </row>
     <row r="10">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>19.17553919670701</v>
+        <v>19.17318026145338</v>
       </c>
     </row>
     <row r="11">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>35.22635810376262</v>
+        <v>35.38840279777597</v>
       </c>
       <c r="F11" t="n">
-        <v>27.85422269477431</v>
+        <v>27.982354844577</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>47.02976189148133</v>
+        <v>47.15553510603037</v>
       </c>
     </row>
     <row r="13">
@@ -1064,11 +1064,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.69942472975451</v>
+        <v>29.84073168889289</v>
       </c>
       <c r="C2" t="n">
-        <v>32.73654523295512</v>
+        <v>32.89551810333118</v>
       </c>
       <c r="D2" t="n">
-        <v>35.77366573615572</v>
+        <v>35.95030451776948</v>
       </c>
       <c r="E2" t="n">
-        <v>38.81078623935633</v>
+        <v>39.00509093220777</v>
       </c>
       <c r="F2" t="n">
-        <v>41.84790674255693</v>
+        <v>42.05987734664605</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.03824046228599</v>
+        <v>31.17954742142437</v>
       </c>
       <c r="C3" t="n">
-        <v>34.0753609654866</v>
+        <v>34.23433383586266</v>
       </c>
       <c r="D3" t="n">
-        <v>37.1124814686872</v>
+        <v>37.28912025030095</v>
       </c>
       <c r="E3" t="n">
-        <v>40.14960197188781</v>
+        <v>40.34390666473925</v>
       </c>
       <c r="F3" t="n">
-        <v>43.18672247508841</v>
+        <v>43.39869307917753</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32.37705619481747</v>
+        <v>32.51836315395585</v>
       </c>
       <c r="C4" t="n">
-        <v>35.41417669801807</v>
+        <v>35.57314956839414</v>
       </c>
       <c r="D4" t="n">
-        <v>38.45129720121868</v>
+        <v>38.62793598283244</v>
       </c>
       <c r="E4" t="n">
-        <v>41.48841770441929</v>
+        <v>41.68272239727074</v>
       </c>
       <c r="F4" t="n">
-        <v>44.52553820761989</v>
+        <v>44.73750881170901</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.71587192734895</v>
+        <v>33.85717888648733</v>
       </c>
       <c r="C5" t="n">
-        <v>36.75299243054955</v>
+        <v>36.91196530092562</v>
       </c>
       <c r="D5" t="n">
-        <v>39.79011293375016</v>
+        <v>39.96675171536391</v>
       </c>
       <c r="E5" t="n">
-        <v>42.82723343695076</v>
+        <v>43.02153812980221</v>
       </c>
       <c r="F5" t="n">
-        <v>45.86435394015137</v>
+        <v>46.07632454424049</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.05468765988043</v>
+        <v>35.19599461901881</v>
       </c>
       <c r="C6" t="n">
-        <v>38.09180816308103</v>
+        <v>38.2507810334571</v>
       </c>
       <c r="D6" t="n">
-        <v>41.12892866628164</v>
+        <v>41.3055674478954</v>
       </c>
       <c r="E6" t="n">
-        <v>44.16604916948225</v>
+        <v>44.3603538623337</v>
       </c>
       <c r="F6" t="n">
-        <v>47.20316967268285</v>
+        <v>47.41514027677198</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>38.54</v>
+        <v>38.72</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>38.69</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>38.73</v>
+        <v>38.91</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55.27902324271707</v>
+        <v>52.02077332262321</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>316781.2469394869</v>
+        <v>276425.7860906069</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.865576440650295</v>
+        <v>2.500524345624524</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52.02077332262321</v>
+        <v>50.90851933383615</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>276425.7860906069</v>
+        <v>262649.8255598647</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.500524345624524</v>
+        <v>2.375908168607694</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>262649.8255598647</v>
+        <v>262649.8255598648</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>262649.8255598648</v>
+        <v>262649.8255598647</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50.90851933383615</v>
+        <v>50.11031353011837</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>262649.8255598647</v>
+        <v>252763.5480025085</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.375908168607694</v>
+        <v>2.286477735689734</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50.11031353011837</v>
+        <v>50.88889132226932</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>252763.5480025085</v>
+        <v>262406.7203740281</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.286477735689734</v>
+        <v>2.373709059601515</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -1294,7 +1294,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50.88889132226932</v>
+        <v>53.91160510356122</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>262406.7203740281</v>
+        <v>299844.9189928687</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.373709059601515</v>
+        <v>2.712371846553135</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53.91160510356122</v>
+        <v>54.29107999385327</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>299844.9189928687</v>
+        <v>304544.95258571</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.712371846553135</v>
+        <v>2.754887954005934</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>304544.95258571</v>
+        <v>304544.9525857099</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>304544.9525857099</v>
+        <v>304544.95258571</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54.29107999385327</v>
+        <v>57.88954878110554</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>304544.95258571</v>
+        <v>349114.2366557583</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.754887954005934</v>
+        <v>3.158057938472149</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>349114.2366557583</v>
+        <v>349114.2366557584</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>57.88954878110554</v>
+        <v>56.37819189045959</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>349114.2366557584</v>
+        <v>330395.1373463381</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.158057938472149</v>
+        <v>2.988726544996339</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56.37819189045959</v>
+        <v>57.65401264230358</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>330395.1373463381</v>
+        <v>346196.9744257189</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.988726544996339</v>
+        <v>3.131668630397997</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>57.65401264230358</v>
+        <v>56.76420945127393</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>346196.9744257189</v>
+        <v>335176.2060011252</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.131668630397997</v>
+        <v>3.031975688784533</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>335176.2060011252</v>
+        <v>335176.2060011251</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56.76420945127393</v>
+        <v>56.66969897621367</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38.62793598283244</v>
+        <v>38.50397142305954</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52.01423065210093</v>
+        <v>51.92762872993299</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.97325064431904</v>
+        <v>34.84169435045542</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47.15553510603037</v>
+        <v>47.04928459246915</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.349869181366118</v>
+        <v>2.344335654578616</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>335176.2060011251</v>
+        <v>333610.7322264906</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.031975688784533</v>
+        <v>3.03527570431284</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>654.780337115778</v>
+        <v>636.9091669619947</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>789.3366637191217</v>
+        <v>800.7119667617043</v>
       </c>
     </row>
     <row r="4">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>246.5585758308463</v>
+        <v>246.1480642011202</v>
       </c>
     </row>
     <row r="7">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>149.9913759902489</v>
+        <v>149.7416454586902</v>
       </c>
     </row>
     <row r="8">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-365.7751924854616</v>
+        <v>-365.1661892501266</v>
       </c>
     </row>
     <row r="9">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-5.260307099910584</v>
+        <v>-5.251548867781903</v>
       </c>
     </row>
     <row r="10">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>1738.170557022656</v>
+        <v>1731.632209217634</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34.97325064431904</v>
+        <v>34.84169435045542</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35.81455261470462</v>
+        <v>35.66657395112342</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.8413019703855866</v>
+        <v>-0.8248796006680053</v>
       </c>
     </row>
   </sheetData>
@@ -843,13 +843,13 @@
         <v>81500</v>
       </c>
       <c r="D2" t="n">
-        <v>3.885378775832521</v>
+        <v>3.885774782116456</v>
       </c>
       <c r="E2" t="n">
-        <v>2.839765143082765</v>
+        <v>2.840042347481519</v>
       </c>
       <c r="F2" t="n">
-        <v>2.766633806305482</v>
+        <v>2.766903871970144</v>
       </c>
     </row>
     <row r="3">
@@ -865,13 +865,13 @@
         <v>99000</v>
       </c>
       <c r="D3" t="n">
-        <v>4.880770789917028</v>
+        <v>4.881166796200963</v>
       </c>
       <c r="E3" t="n">
-        <v>3.536539552941919</v>
+        <v>3.536816757340674</v>
       </c>
       <c r="F3" t="n">
-        <v>3.356734793969791</v>
+        <v>3.356997904741327</v>
       </c>
     </row>
     <row r="4">
@@ -887,13 +887,13 @@
         <v>92000</v>
       </c>
       <c r="D4" t="n">
-        <v>4.429032395550832</v>
+        <v>4.429428401834766</v>
       </c>
       <c r="E4" t="n">
-        <v>3.220322676885582</v>
+        <v>3.220599881284336</v>
       </c>
       <c r="F4" t="n">
-        <v>2.977879747790682</v>
+        <v>2.978136082775673</v>
       </c>
     </row>
     <row r="5">
@@ -909,13 +909,13 @@
         <v>67500</v>
       </c>
       <c r="D5" t="n">
-        <v>3.142397370902944</v>
+        <v>3.142793377186878</v>
       </c>
       <c r="E5" t="n">
-        <v>2.319678159632061</v>
+        <v>2.319955364030815</v>
       </c>
       <c r="F5" t="n">
-        <v>2.089800143812667</v>
+        <v>2.090049877505238</v>
       </c>
     </row>
     <row r="6">
@@ -931,13 +931,13 @@
         <v>60000</v>
       </c>
       <c r="D6" t="n">
-        <v>2.764761173719845</v>
+        <v>2.76515718000378</v>
       </c>
       <c r="E6" t="n">
-        <v>2.055332821603892</v>
+        <v>2.055610026002646</v>
       </c>
       <c r="F6" t="n">
-        <v>1.803966357560469</v>
+        <v>1.804209659961064</v>
       </c>
     </row>
     <row r="7">
@@ -953,13 +953,13 @@
         <v>78000</v>
       </c>
       <c r="D7" t="n">
-        <v>3.600370325128296</v>
+        <v>3.600766331412231</v>
       </c>
       <c r="E7" t="n">
-        <v>2.640259227589807</v>
+        <v>2.640536431988562</v>
       </c>
       <c r="F7" t="n">
-        <v>2.257678519573137</v>
+        <v>2.25791555630425</v>
       </c>
     </row>
     <row r="8">
@@ -975,13 +975,13 @@
         <v>81500</v>
       </c>
       <c r="D8" t="n">
-        <v>3.874512828649423</v>
+        <v>3.874908834933357</v>
       </c>
       <c r="E8" t="n">
-        <v>2.832158980054596</v>
+        <v>2.83243618445335</v>
       </c>
       <c r="F8" t="n">
-        <v>2.359404565532478</v>
+        <v>2.35963549795139</v>
       </c>
     </row>
     <row r="9">
@@ -997,13 +997,13 @@
         <v>56500</v>
       </c>
       <c r="D9" t="n">
-        <v>2.576299335691676</v>
+        <v>2.576695341975611</v>
       </c>
       <c r="E9" t="n">
-        <v>1.923409534984173</v>
+        <v>1.923686739382928</v>
       </c>
       <c r="F9" t="n">
-        <v>1.561082326908671</v>
+        <v>1.561307312217294</v>
       </c>
     </row>
     <row r="10">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>19.17318026145338</v>
+        <v>19.17515576342638</v>
       </c>
     </row>
     <row r="11">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>35.38840279777597</v>
+        <v>35.25153276477852</v>
       </c>
       <c r="F11" t="n">
-        <v>27.982354844577</v>
+        <v>27.87412882904277</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>47.15553510603037</v>
+        <v>47.04928459246915</v>
       </c>
     </row>
     <row r="13">
@@ -1066,7 +1066,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.84073168889289</v>
+        <v>29.74156344629416</v>
       </c>
       <c r="C2" t="n">
-        <v>32.89551810333118</v>
+        <v>32.78395170214537</v>
       </c>
       <c r="D2" t="n">
-        <v>35.95030451776948</v>
+        <v>35.82633995799658</v>
       </c>
       <c r="E2" t="n">
-        <v>39.00509093220777</v>
+        <v>38.86872821384779</v>
       </c>
       <c r="F2" t="n">
-        <v>42.05987734664605</v>
+        <v>41.911116469699</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.17954742142437</v>
+        <v>31.08037917882564</v>
       </c>
       <c r="C3" t="n">
-        <v>34.23433383586266</v>
+        <v>34.12276743467685</v>
       </c>
       <c r="D3" t="n">
-        <v>37.28912025030095</v>
+        <v>37.16515569052805</v>
       </c>
       <c r="E3" t="n">
-        <v>40.34390666473925</v>
+        <v>40.20754394637927</v>
       </c>
       <c r="F3" t="n">
-        <v>43.39869307917753</v>
+        <v>43.24993220223048</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32.51836315395585</v>
+        <v>32.41919491135712</v>
       </c>
       <c r="C4" t="n">
-        <v>35.57314956839414</v>
+        <v>35.46158316720833</v>
       </c>
       <c r="D4" t="n">
-        <v>38.62793598283244</v>
+        <v>38.50397142305954</v>
       </c>
       <c r="E4" t="n">
-        <v>41.68272239727074</v>
+        <v>41.54635967891075</v>
       </c>
       <c r="F4" t="n">
-        <v>44.73750881170901</v>
+        <v>44.58874793476195</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.85717888648733</v>
+        <v>33.7580106438886</v>
       </c>
       <c r="C5" t="n">
-        <v>36.91196530092562</v>
+        <v>36.8003988997398</v>
       </c>
       <c r="D5" t="n">
-        <v>39.96675171536391</v>
+        <v>39.84278715559101</v>
       </c>
       <c r="E5" t="n">
-        <v>43.02153812980221</v>
+        <v>42.88517541144223</v>
       </c>
       <c r="F5" t="n">
-        <v>46.07632454424049</v>
+        <v>45.92756366729344</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.19599461901881</v>
+        <v>35.09682637642008</v>
       </c>
       <c r="C6" t="n">
-        <v>38.2507810334571</v>
+        <v>38.13921463227129</v>
       </c>
       <c r="D6" t="n">
-        <v>41.3055674478954</v>
+        <v>41.1816028881225</v>
       </c>
       <c r="E6" t="n">
-        <v>44.3603538623337</v>
+        <v>44.22399114397371</v>
       </c>
       <c r="F6" t="n">
-        <v>47.41514027677198</v>
+        <v>47.26637939982491</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>38.72</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>38.86</v>
+        <v>38.74</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>38.91</v>
+        <v>38.78</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56.66969897621367</v>
+        <v>57.74091043680599</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>333610.7322264906</v>
+        <v>346802.0301858037</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.03527570431284</v>
+        <v>3.155293504510801</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>346802.0301858037</v>
+        <v>346802.0301858036</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>57.74091043680599</v>
+        <v>60.27523998991467</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>346802.0301858036</v>
+        <v>378010.7107236903</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.155293504510801</v>
+        <v>3.439238056198658</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60.27523998991467</v>
+        <v>62.78997421142714</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>378010.7107236903</v>
+        <v>408978.0870306143</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.439238056198658</v>
+        <v>3.720987160321921</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62.78997421142714</v>
+        <v>60.36015309349821</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>408978.0870306143</v>
+        <v>379056.3623911969</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.720987160321921</v>
+        <v>3.448751662311912</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>379056.3623911969</v>
+        <v>379056.362391197</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>379056.362391197</v>
+        <v>379056.3623911969</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60.36015309349821</v>
+        <v>61.20482670023672</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38.50397142305954</v>
+        <v>39.75850279712702</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51.92762872993299</v>
+        <v>52.65429848142863</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.84169435045542</v>
+        <v>36.25957636038456</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47.04928459246915</v>
+        <v>47.92266448285943</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.344335654578616</v>
+        <v>2.361828051711729</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>379056.3623911969</v>
+        <v>380065.3318954653</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.448751662311912</v>
+        <v>3.402831478073339</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>636.9091669619947</v>
+        <v>707.0214507762394</v>
       </c>
     </row>
     <row r="3">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>246.1480642011202</v>
+        <v>249.5926342117098</v>
       </c>
     </row>
     <row r="7">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>149.7416454586902</v>
+        <v>151.8371142285031</v>
       </c>
     </row>
     <row r="8">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-365.1661892501266</v>
+        <v>-370.2762863311443</v>
       </c>
     </row>
     <row r="9">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-5.251548867781903</v>
+        <v>-5.325038487933159</v>
       </c>
     </row>
     <row r="10">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>1731.632209217634</v>
+        <v>1802.100945111113</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34.84169435045542</v>
+        <v>36.25957636038456</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35.66657395112342</v>
+        <v>37.1492006395328</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.8248796006680053</v>
+        <v>-0.8896242791482436</v>
       </c>
     </row>
   </sheetData>
@@ -843,13 +843,13 @@
         <v>81500</v>
       </c>
       <c r="D2" t="n">
-        <v>3.885774782116456</v>
+        <v>3.882451925293722</v>
       </c>
       <c r="E2" t="n">
-        <v>2.840042347481519</v>
+        <v>2.837716347705605</v>
       </c>
       <c r="F2" t="n">
-        <v>2.766903871970144</v>
+        <v>2.76463777273684</v>
       </c>
     </row>
     <row r="3">
@@ -865,13 +865,13 @@
         <v>99000</v>
       </c>
       <c r="D3" t="n">
-        <v>4.881166796200963</v>
+        <v>4.877843939378229</v>
       </c>
       <c r="E3" t="n">
-        <v>3.536816757340674</v>
+        <v>3.53449075756476</v>
       </c>
       <c r="F3" t="n">
-        <v>3.356997904741327</v>
+        <v>3.3547901634559</v>
       </c>
     </row>
     <row r="4">
@@ -887,13 +887,13 @@
         <v>92000</v>
       </c>
       <c r="D4" t="n">
-        <v>4.429428401834766</v>
+        <v>4.426105545012032</v>
       </c>
       <c r="E4" t="n">
-        <v>3.220599881284336</v>
+        <v>3.218273881508422</v>
       </c>
       <c r="F4" t="n">
-        <v>2.978136082775673</v>
+        <v>2.975985196569214</v>
       </c>
     </row>
     <row r="5">
@@ -909,13 +909,13 @@
         <v>67500</v>
       </c>
       <c r="D5" t="n">
-        <v>3.142793377186878</v>
+        <v>3.139470520364144</v>
       </c>
       <c r="E5" t="n">
-        <v>2.319955364030815</v>
+        <v>2.317629364254901</v>
       </c>
       <c r="F5" t="n">
-        <v>2.090049877505238</v>
+        <v>2.087954382211622</v>
       </c>
     </row>
     <row r="6">
@@ -931,13 +931,13 @@
         <v>60000</v>
       </c>
       <c r="D6" t="n">
-        <v>2.76515718000378</v>
+        <v>2.761834323181046</v>
       </c>
       <c r="E6" t="n">
-        <v>2.055610026002646</v>
+        <v>2.053284026226732</v>
       </c>
       <c r="F6" t="n">
-        <v>1.804209659961064</v>
+        <v>1.802168129120251</v>
       </c>
     </row>
     <row r="7">
@@ -953,13 +953,13 @@
         <v>78000</v>
       </c>
       <c r="D7" t="n">
-        <v>3.600766331412231</v>
+        <v>3.597443474589496</v>
       </c>
       <c r="E7" t="n">
-        <v>2.640536431988562</v>
+        <v>2.638210432212647</v>
       </c>
       <c r="F7" t="n">
-        <v>2.25791555630425</v>
+        <v>2.255926600191252</v>
       </c>
     </row>
     <row r="8">
@@ -975,13 +975,13 @@
         <v>81500</v>
       </c>
       <c r="D8" t="n">
-        <v>3.874908834933357</v>
+        <v>3.871585978110623</v>
       </c>
       <c r="E8" t="n">
-        <v>2.83243618445335</v>
+        <v>2.830110184677436</v>
       </c>
       <c r="F8" t="n">
-        <v>2.35963549795139</v>
+        <v>2.357697762630256</v>
       </c>
     </row>
     <row r="9">
@@ -997,13 +997,13 @@
         <v>56500</v>
       </c>
       <c r="D9" t="n">
-        <v>2.576695341975611</v>
+        <v>2.573372485152877</v>
       </c>
       <c r="E9" t="n">
-        <v>1.923686739382928</v>
+        <v>1.921360739607013</v>
       </c>
       <c r="F9" t="n">
-        <v>1.561307312217294</v>
+        <v>1.559419478619441</v>
       </c>
     </row>
     <row r="10">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>19.17515576342638</v>
+        <v>19.15857948553477</v>
       </c>
     </row>
     <row r="11">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>35.25153276477852</v>
+        <v>36.37703229941216</v>
       </c>
       <c r="F11" t="n">
-        <v>27.87412882904277</v>
+        <v>28.76408499732466</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>47.04928459246915</v>
+        <v>47.92266448285943</v>
       </c>
     </row>
     <row r="13">
@@ -1065,8 +1065,8 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.74156344629416</v>
+        <v>30.74515997262496</v>
       </c>
       <c r="C2" t="n">
-        <v>32.78395170214537</v>
+        <v>33.91301565234452</v>
       </c>
       <c r="D2" t="n">
-        <v>35.82633995799658</v>
+        <v>37.08087133206406</v>
       </c>
       <c r="E2" t="n">
-        <v>38.86872821384779</v>
+        <v>40.24872701178361</v>
       </c>
       <c r="F2" t="n">
-        <v>41.911116469699</v>
+        <v>43.41658269150317</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.08037917882564</v>
+        <v>32.08397570515645</v>
       </c>
       <c r="C3" t="n">
-        <v>34.12276743467685</v>
+        <v>35.251831384876</v>
       </c>
       <c r="D3" t="n">
-        <v>37.16515569052805</v>
+        <v>38.41968706459554</v>
       </c>
       <c r="E3" t="n">
-        <v>40.20754394637927</v>
+        <v>41.58754274431509</v>
       </c>
       <c r="F3" t="n">
-        <v>43.24993220223048</v>
+        <v>44.75539842403465</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32.41919491135712</v>
+        <v>33.42279143768792</v>
       </c>
       <c r="C4" t="n">
-        <v>35.46158316720833</v>
+        <v>36.59064711740748</v>
       </c>
       <c r="D4" t="n">
-        <v>38.50397142305954</v>
+        <v>39.75850279712702</v>
       </c>
       <c r="E4" t="n">
-        <v>41.54635967891075</v>
+        <v>42.92635847684657</v>
       </c>
       <c r="F4" t="n">
-        <v>44.58874793476195</v>
+        <v>46.09421415656612</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.7580106438886</v>
+        <v>34.76160717021941</v>
       </c>
       <c r="C5" t="n">
-        <v>36.8003988997398</v>
+        <v>37.92946284993896</v>
       </c>
       <c r="D5" t="n">
-        <v>39.84278715559101</v>
+        <v>41.09731852965849</v>
       </c>
       <c r="E5" t="n">
-        <v>42.88517541144223</v>
+        <v>44.26517420937806</v>
       </c>
       <c r="F5" t="n">
-        <v>45.92756366729344</v>
+        <v>47.4330298890976</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.09682637642008</v>
+        <v>36.10042290275089</v>
       </c>
       <c r="C6" t="n">
-        <v>38.13921463227129</v>
+        <v>39.26827858247044</v>
       </c>
       <c r="D6" t="n">
-        <v>41.1816028881225</v>
+        <v>42.43613426218998</v>
       </c>
       <c r="E6" t="n">
-        <v>44.22399114397371</v>
+        <v>45.60398994190953</v>
       </c>
       <c r="F6" t="n">
-        <v>47.26637939982491</v>
+        <v>48.77184562162908</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>38.6</v>
+        <v>39.85</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>38.74</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>38.78</v>
+        <v>40.04</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61.20482670023672</v>
+        <v>60.02703358191058</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.75850279712702</v>
+        <v>37.59459096650158</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52.65429848142863</v>
+        <v>51.64104717846436</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36.25957636038456</v>
+        <v>36.57486012271121</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47.92266448285943</v>
+        <v>39.9739629353458</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61250</v>
+        <v>58050</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85000</v>
+        <v>88475</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.361828051711729</v>
+        <v>2.227855810341818</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>380065.3318954653</v>
+        <v>469117.6939585244</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.402831478073339</v>
+        <v>4.480893908321272</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>707.0214507762394</v>
+        <v>689.9266420652223</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>800.7119667617043</v>
+        <v>776.3211072602011</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>182.1631039520335</v>
+        <v>175.5384612140754</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>86.376</v>
+        <v>102.209</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>249.5926342117098</v>
+        <v>265.9332049273179</v>
       </c>
     </row>
     <row r="7">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>151.8371142285031</v>
+        <v>183.5978885372312</v>
       </c>
     </row>
     <row r="8">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-370.2762863311443</v>
+        <v>-365.3522891261293</v>
       </c>
     </row>
     <row r="9">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-5.325038487933159</v>
+        <v>-4.64054894393647</v>
       </c>
     </row>
     <row r="10">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>1802.100945111113</v>
+        <v>1823.533465933982</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>49700000</v>
+        <v>49857565</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>36.25957636038456</v>
+        <v>36.57486012271121</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37.1492006395328</v>
+        <v>37.43518087492047</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.8896242791482436</v>
+        <v>-0.8603207522092617</v>
       </c>
     </row>
   </sheetData>
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81500</v>
+        <v>118900</v>
       </c>
       <c r="C2" t="n">
-        <v>81500</v>
+        <v>118900</v>
       </c>
       <c r="D2" t="n">
-        <v>3.882451925293722</v>
+        <v>5.001860254640563</v>
       </c>
       <c r="E2" t="n">
-        <v>2.837716347705605</v>
+        <v>3.621302178248394</v>
       </c>
       <c r="F2" t="n">
-        <v>2.76463777273684</v>
+        <v>3.528044230556882</v>
       </c>
     </row>
     <row r="3">
@@ -859,19 +859,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>99000</v>
+        <v>118900</v>
       </c>
       <c r="C3" t="n">
-        <v>99000</v>
+        <v>118900</v>
       </c>
       <c r="D3" t="n">
-        <v>4.877843939378229</v>
+        <v>5.001860254640563</v>
       </c>
       <c r="E3" t="n">
-        <v>3.53449075756476</v>
+        <v>3.621302178248394</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3547901634559</v>
+        <v>3.437187917520405</v>
       </c>
     </row>
     <row r="4">
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>92000</v>
+        <v>58050</v>
       </c>
       <c r="C4" t="n">
-        <v>92000</v>
+        <v>58050</v>
       </c>
       <c r="D4" t="n">
-        <v>4.426105545012032</v>
+        <v>2.582008112142228</v>
       </c>
       <c r="E4" t="n">
-        <v>3.218273881508422</v>
+        <v>1.92740567849956</v>
       </c>
       <c r="F4" t="n">
-        <v>2.975985196569214</v>
+        <v>1.782300381566553</v>
       </c>
     </row>
     <row r="5">
@@ -903,19 +903,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67500</v>
+        <v>58050</v>
       </c>
       <c r="C5" t="n">
-        <v>67500</v>
+        <v>58050</v>
       </c>
       <c r="D5" t="n">
-        <v>3.139470520364144</v>
+        <v>2.582008112142228</v>
       </c>
       <c r="E5" t="n">
-        <v>2.317629364254901</v>
+        <v>1.92740567849956</v>
       </c>
       <c r="F5" t="n">
-        <v>2.087954382211622</v>
+        <v>1.736401512161766</v>
       </c>
     </row>
     <row r="6">
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60000</v>
+        <v>26950</v>
       </c>
       <c r="C6" t="n">
-        <v>60000</v>
+        <v>26950</v>
       </c>
       <c r="D6" t="n">
-        <v>2.761834323181046</v>
+        <v>1.004624195629258</v>
       </c>
       <c r="E6" t="n">
-        <v>2.053284026226732</v>
+        <v>0.8232369369404803</v>
       </c>
       <c r="F6" t="n">
-        <v>1.802168129120251</v>
+        <v>0.7225553559655875</v>
       </c>
     </row>
     <row r="7">
@@ -947,19 +947,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78000</v>
+        <v>26950</v>
       </c>
       <c r="C7" t="n">
-        <v>78000</v>
+        <v>26950</v>
       </c>
       <c r="D7" t="n">
-        <v>3.597443474589496</v>
+        <v>1.004624195629258</v>
       </c>
       <c r="E7" t="n">
-        <v>2.638210432212647</v>
+        <v>0.8232369369404803</v>
       </c>
       <c r="F7" t="n">
-        <v>2.255926600191252</v>
+        <v>0.7039476766629302</v>
       </c>
     </row>
     <row r="8">
@@ -969,19 +969,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81500</v>
+        <v>26950</v>
       </c>
       <c r="C8" t="n">
-        <v>81500</v>
+        <v>26950</v>
       </c>
       <c r="D8" t="n">
-        <v>3.871585978110623</v>
+        <v>1.004624195629258</v>
       </c>
       <c r="E8" t="n">
-        <v>2.830110184677436</v>
+        <v>0.8232369369404803</v>
       </c>
       <c r="F8" t="n">
-        <v>2.357697762630256</v>
+        <v>0.6858191934885305</v>
       </c>
     </row>
     <row r="9">
@@ -991,19 +991,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56500</v>
+        <v>26950</v>
       </c>
       <c r="C9" t="n">
-        <v>56500</v>
+        <v>26950</v>
       </c>
       <c r="D9" t="n">
-        <v>2.573372485152877</v>
+        <v>1.004624195629258</v>
       </c>
       <c r="E9" t="n">
-        <v>1.921360739607013</v>
+        <v>0.8232369369404803</v>
       </c>
       <c r="F9" t="n">
-        <v>1.559419478619441</v>
+        <v>0.668157565896015</v>
       </c>
     </row>
     <row r="10">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>19.15857948553477</v>
+        <v>13.26441383381867</v>
       </c>
     </row>
     <row r="11">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>36.37703229941216</v>
+        <v>33.77872546473692</v>
       </c>
       <c r="F11" t="n">
-        <v>28.76408499732466</v>
+        <v>26.70954910152713</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>47.92266448285943</v>
+        <v>39.9739629353458</v>
       </c>
     </row>
     <row r="13">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>85000</v>
+        <v>88475</v>
       </c>
     </row>
   </sheetData>
@@ -1065,7 +1065,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.74515997262496</v>
+        <v>29.46476473118788</v>
       </c>
       <c r="C2" t="n">
-        <v>33.91301565234452</v>
+        <v>32.56301052690554</v>
       </c>
       <c r="D2" t="n">
-        <v>37.08087133206406</v>
+        <v>35.66125632262321</v>
       </c>
       <c r="E2" t="n">
-        <v>40.24872701178361</v>
+        <v>38.75950211834088</v>
       </c>
       <c r="F2" t="n">
-        <v>43.41658269150317</v>
+        <v>41.85774791405854</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.08397570515645</v>
+        <v>30.43143205312707</v>
       </c>
       <c r="C3" t="n">
-        <v>35.251831384876</v>
+        <v>33.52967784884473</v>
       </c>
       <c r="D3" t="n">
-        <v>38.41968706459554</v>
+        <v>36.6279236445624</v>
       </c>
       <c r="E3" t="n">
-        <v>41.58754274431509</v>
+        <v>39.72616944028007</v>
       </c>
       <c r="F3" t="n">
-        <v>44.75539842403465</v>
+        <v>42.82441523599773</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33.42279143768792</v>
+        <v>31.39809937506625</v>
       </c>
       <c r="C4" t="n">
-        <v>36.59064711740748</v>
+        <v>34.49634517078392</v>
       </c>
       <c r="D4" t="n">
-        <v>39.75850279712702</v>
+        <v>37.59459096650158</v>
       </c>
       <c r="E4" t="n">
-        <v>42.92635847684657</v>
+        <v>40.69283676221925</v>
       </c>
       <c r="F4" t="n">
-        <v>46.09421415656612</v>
+        <v>43.79108255793692</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34.76160717021941</v>
+        <v>32.36476669700544</v>
       </c>
       <c r="C5" t="n">
-        <v>37.92946284993896</v>
+        <v>35.4630124927231</v>
       </c>
       <c r="D5" t="n">
-        <v>41.09731852965849</v>
+        <v>38.56125828844077</v>
       </c>
       <c r="E5" t="n">
-        <v>44.26517420937806</v>
+        <v>41.65950408415843</v>
       </c>
       <c r="F5" t="n">
-        <v>47.4330298890976</v>
+        <v>44.7577498798761</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.10042290275089</v>
+        <v>33.33143401894463</v>
       </c>
       <c r="C6" t="n">
-        <v>39.26827858247044</v>
+        <v>36.42967981466229</v>
       </c>
       <c r="D6" t="n">
-        <v>42.43613426218998</v>
+        <v>39.52792561037995</v>
       </c>
       <c r="E6" t="n">
-        <v>45.60398994190953</v>
+        <v>42.62617140609763</v>
       </c>
       <c r="F6" t="n">
-        <v>48.77184562162908</v>
+        <v>45.72441720181529</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>39.85</v>
+        <v>37.67</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>39.99</v>
+        <v>37.79</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>40.04</v>
+        <v>37.82</v>
       </c>
     </row>
   </sheetData>
@@ -1294,7 +1294,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $488,900/day is 12.2x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60.02703358191058</v>
+        <v>60.00754639429606</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>469117.6939585244</v>
+        <v>468801.1160977064</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.480893908321272</v>
+        <v>4.477870036430875</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60.00754639429606</v>
+        <v>63.04105193295555</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>468801.1160977064</v>
+        <v>518081.7364317181</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.477870036430875</v>
+        <v>4.948586094036006</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63.04105193295555</v>
+        <v>64.34019777392321</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>518081.7364317181</v>
+        <v>539186.9271529223</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.948586094036006</v>
+        <v>5.150177553395805</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64.34019777392321</v>
+        <v>64.18430027300708</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>539186.9271529223</v>
+        <v>536654.3042663776</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.150177553395805</v>
+        <v>5.125986578272627</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>536654.3042663776</v>
+        <v>536654.3042663777</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/insw_fv_report.xlsx
+++ b/outputs/insw_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>536654.3042663777</v>
+        <v>536654.3042663776</v>
       </c>
     </row>
     <row r="16">
